--- a/aq_files/0076.xlsx
+++ b/aq_files/0076.xlsx
@@ -1,107 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Scenario Question</t>
-  </si>
-  <si>
-    <t>A researcher selects 50 students randomly from a list of 500 students. What type of sampling method is this?</t>
-  </si>
-  <si>
-    <t>A survey selects every 10th person from a list. Is this simple random sampling? Explain.</t>
-  </si>
-  <si>
-    <t>A researcher uses a random number generator to pick participants. What sampling technique is being used?</t>
-  </si>
-  <si>
-    <t>A population is divided into groups, and random samples are taken from each group. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A researcher selects participants randomly but ensures equal representation from categories. What method is this?</t>
-  </si>
-  <si>
-    <t>A lottery method is used to select individuals from a population. Identify the sampling technique.</t>
-  </si>
-  <si>
-    <t>A company randomly selects customers for feedback without any grouping. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A researcher selects clusters randomly and studies all members within selected clusters. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A population is divided into strata, but samples are not randomly chosen. Is this random sampling? Why or why not?</t>
-  </si>
-  <si>
-    <t>A researcher uses systematic selection (every 5th item). Is this truly random sampling? Explain.</t>
-  </si>
-  <si>
-    <t>A dataset is created by randomly picking individuals, but some groups are underrepresented. What issue arises here?</t>
-  </si>
-  <si>
-    <t>A researcher ensures each individual has an equal chance of selection. What principle of sampling is this?</t>
-  </si>
-  <si>
-    <t>A sample is drawn randomly but is too small to represent the population. What problem may occur?</t>
-  </si>
-  <si>
-    <t>A researcher repeats random sampling multiple times. What is this process called and why is it useful?</t>
-  </si>
-  <si>
-    <t>A population is large and scattered geographically. Which random sampling method would be suitable?</t>
-  </si>
-  <si>
-    <t>A researcher randomly selects schools and then students within them. What sampling technique is this?</t>
-  </si>
-  <si>
-    <t>A sample is selected randomly, but bias still appears in results. What could be the reason?</t>
-  </si>
-  <si>
-    <t>A researcher compares results from random sampling and non-random sampling. What difference is expected?</t>
-  </si>
-  <si>
-    <t>A study requires unbiased representation of the population. Why is random sampling important here?</t>
-  </si>
-  <si>
-    <t>A researcher uses computer software to randomly pick data points. What advantage does this provide?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -111,32 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -334,118 +316,1063 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task_ID,Task_Name,Pair_RDD_Operation,Operation_Type,PySpark_Code_Snippet,Input_Records,Unique_Keys,Output_Records,Execution_Time_Sec,Partitions,Shuffle_Read_MB,Shuffle_Write_MB,Memory_MB,Data_Skew,Use_Case</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-001,Create_Pair_RDD,map,Create,rdd.map(lambda x: (x[0], x[1])),10000000,5000000,10000000,18,8,0,0,2048,No,Convert to key-value pairs</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-002,Count_By_Key,countByKey,Action,rdd.countByKey(),10000000,5000000,5000000,22,8,1280,960,3072,No,Count occurrences per key</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-003,Group_By_Key,groupByKey,Transformation,rdd.groupByKey(),12000000,3000000,8000000,45,12,2560,1920,4096,Yes,Group values by key</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-004,Reduce_By_Key,reduceByKey,Transformation,rdd.reduceByKey(lambda a,b: a+b),12000000,3000000,3000000,28,8,1920,1280,3072,No,Reduce with map-side combine</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-005,Combine_By_Key,combineByKey,Transformation,rdd.combineByKey(create, merge, combine),15000000,4000000,4000000,35,12,2560,1920,4096,No,Advanced aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-006,Aggregate_By_Key,aggregateByKey,Transformation,rdd.aggregateByKey(0, lambda a,b: a+b, lambda a,b: a+b),12000000,3000000,3000000,32,8,1920,1280,3072,No,Aggregate with initial value</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-007,Fold_By_Key,foldByKey,Transformation,rdd.foldByKey(0, lambda a,b: a+b),12000000,3000000,3000000,30,8,1920,1280,3072,No,Fold with zero value</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-008,Sort_By_Key,sortByKey,Transformation,rdd.sortByKey(),18000000,5000000,18000000,68,16,3840,3840,4096,Yes,Sort by keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-009,Map_Values,mapValues,Transformation,rdd.mapValues(lambda v: v*2),10000000,5000000,10000000,12,8,0,0,2048,No,Apply to values only</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-010,FlatMap_Values,flatMapValues,Transformation,rdd.flatMapValues(lambda v: v.split()),8000000,2000000,24000000,28,12,0,0,3072,No,Transform values to multiple</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-011,Keys,keys,Transformation,rdd.keys(),10000000,5000000,10000000,5,8,0,0,1024,No,Extract keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-012,Values,values,Transformation,rdd.values(),10000000,5000000,10000000,5,8,0,0,1024,No,Extract values</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-013,Join,join,Transformation,rdd1.join(rdd2),20000000,4000000,15000000,120,32,5120,3840,8192,Yes,Inner join</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-014,Left_Outer_Join,leftOuterJoin,Transformation,rdd1.leftOuterJoin(rdd2),20000000,4000000,18000000,125,32,5120,3840,8192,Yes,Left outer join</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-015,Right_Outer_Join,rightOuterJoin,Transformation,rdd1.rightOuterJoin(rdd2),20000000,4000000,18000000,125,32,5120,3840,8192,Yes,Right outer join</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-016,Full_Outer_Join,fullOuterJoin,Transformation,rdd1.fullOuterJoin(rdd2),20000000,4000000,20000000,130,32,5120,3840,8192,Yes,Full outer join</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-017,Cogroup,cogroup,Transformation,rdd1.cogroup(rdd2),22000000,4000000,18000000,85,32,7680,5120,10240,Yes,Co-group multiple RDDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-018,Subtract_By_Key,subtractByKey,Transformation,rdd1.subtractByKey(rdd2),15000000,3000000,10000000,45,16,2560,1920,4096,No,Remove keys present in other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-019,Group_With,groupWith,Transformation,rdd1.groupWith(rdd2),22000000,4000000,18000000,88,32,7680,5120,10240,Yes,Group multiple RDDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-020,Lookup,lookup,Action,rdd.lookup(key),10000000,5000000,1,8,8,0,0,512,No,Get values for specific key</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-021,Count_Approx,countApprox,Action,rdd.countApprox(timeout),10000000,5000000,1,5,8,0,0,512,No,Approximate count</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-022,Count_By_Key_Approx,countApproxDistinctByKey,Action,rdd.countApproxDistinctByKey(),12000000,3000000,3000000,25,8,1280,960,2048,No,Approximate distinct count per key</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-023,Reduce_By_Key_Local,reduceByKeyLocally,Action,rdd.reduceByKeyLocally(lambda a,b: a+b),12000000,3000000,3000000,18,8,1280,960,4096,No,Reduce to local map</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-024,Combine_By_Key_Agg,combineByKey,Transformation,rdd.combineByKey(lambda v: (v,1), lambda a,b: (a[0]+b, a[1]+1), lambda a,b: (a[0]+b[0], a[1]+b[1])),15000000,4000000,4000000,42,16,2560,1920,5120,No,Calculate sum and count</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-025,Aggregate_Complex,aggregateByKey,Transformation,rdd.aggregateByKey((0,0), lambda a,b: (a[0]+b, a[1]+1), lambda a,b: (a[0]+b[0], a[1]+b[1])),15000000,4000000,4000000,45,16,2560,1920,5120,No,Complex aggregation</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-026,Group_By_Key_Optimized,groupByKey,Transformation,rdd.groupByKey(numPartitions=64),12000000,3000000,8000000,52,64,2560,1920,4096,Yes,Optimized partitioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-027,Reduce_By_Key_Partitioned,reduceByKey,Transformation,rdd.reduceByKey(lambda a,b: a+b, numPartitions=64),12000000,3000000,3000000,35,64,1920,1280,4096,No,Partitioned reduce</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-028,Join_Optimized,join,Transformation,rdd1.join(rdd2, numPartitions=64),20000000,4000000,15000000,95,64,5120,3840,8192,Yes,Optimized join</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-029,Partition_By,partitionBy,Transformation,rdd.partitionBy(16, hash),10000000,5000000,10000000,25,16,0,1280,3072,No,Repartition by key</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>PRDD-030,Repartition_And_Sort,repartitionAndSortWithinPartitions,Transformation,rdd.repartitionAndSortWithinPartitions(16),18000000,5000000,18000000,52,16,3840,3840,4096,Yes,Repartition and sort</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What are Pair RDDs? How do you create them? Provide code examples from the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze PRDD-001 | Pair RDDs are RDDs of key-value pairs. Created via: rdd.map(lambda x: (x[0], x[1])), or using sc.parallelize([(k1,v1), (k2,v2)])</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Pair RDDs enable key-based operations like grouping, aggregation, joins</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What is countByKey? Write code to count occurrences per key.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-002 | counts = rdd.countByKey() -&gt; returns dictionary of key:count. Action that returns to driver</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>countByKey is an action; useful for understanding key distribution</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between groupByKey and reduceByKey? Compare performance from dataset.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Compare PRDD-003 and PRDD-004 | groupByKey: 45s, 2.5GB shuffle, 8M output; reduceByKey: 28s, 1.9GB shuffle, 3M output. reduceByKey 38% faster</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>reduceByKey does map-side aggregation; groupByKey does not</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Write code to sum values by key using reduceByKey.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-004 | sum_by_key = rdd.reduceByKey(lambda a, b: a + b); result = sum_by_key.collect()</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>reduceByKey performs local aggregation before shuffle</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is combineByKey? When would you use it? Provide example.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-005 | combineByKey used for complex aggregations: rdd.combineByKey(lambda v: (v,1), lambda a,b: (a[0]+b, a[1]+1), lambda a,b: (a[0]+b[0], a[1]+b[1]))</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>combineByKey provides flexibility for custom aggregation logic</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Write code to calculate sum and count per key using combineByKey.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-024 | sum_count = rdd.combineByKey(lambda v: (v,1), lambda a,b: (a[0]+b, a[1]+1), lambda a,b: (a[0]+b[0], a[1]+b[1]))</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>combineByKey can compute multiple aggregates in one pass</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is aggregateByKey? How does it differ from reduceByKey?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-006 | aggregateByKey allows different initial value and two aggregation functions: rdd.aggregateByKey(0, lambda a,b: a+b, lambda a,b: a+b)</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>aggregateByKey provides per-partition and inter-partition aggregation</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Write code to find average value per key using aggregateByKey.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-025 | avg = rdd.aggregateByKey((0,0), lambda a,b: (a[0]+b, a[1]+1), lambda a,b: (a[0]+b[0], a[1]+b[1])).mapValues(lambda v: v[0]/v[1])</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>aggregateByKey can compute averages, sums, and counts in one pass</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is foldByKey? How is it different from reduceByKey?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-007 | foldByKey uses a zero value: rdd.foldByKey(0, lambda a,b: a+b). Zero value must be identity for operation</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>foldByKey is similar to reduceByKey but with a zero value</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is mapValues? Write code to transform values only.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-009 | transformed = rdd.mapValues(lambda v: v * 2). mapValues preserves keys and transforms values</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>mapValues is more efficient than map for key-value pairs</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What is flatMapValues? When would you use it?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-010 | exploded = rdd.flatMapValues(lambda v: v.split()). Useful for expanding values into multiple records</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>flatMapValues creates multiple output records per input value</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Write code to extract only keys and only values from a Pair RDD.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-011, PRDD-012 | keys_rdd = rdd.keys(); values_rdd = rdd.values(); both are transformations</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>keys() and values() are useful for filtering and analysis</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What are the different join types in Pair RDDs? Provide code examples.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-013 to PRDD-016 | inner = rdd1.join(rdd2); left = rdd1.leftOuterJoin(rdd2); right = rdd1.rightOuterJoin(rdd2); full = rdd1.fullOuterJoin(rdd2)</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Different join types handle missing keys differently</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What is cogroup? How is it different from join?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-017 | cogroup groups values from multiple RDDs by key: rdd1.cogroup(rdd2). Returns all values for each key</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>cogroup is the building block for joins; groups without flattening</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Write code to remove keys present in another RDD using subtractByKey.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-018 | filtered = rdd1.subtractByKey(rdd2). Removes all keys from rdd1 that exist in rdd2</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>subtractByKey is useful for data cleaning and filtering</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is lookup? How does it work? Provide example.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-020 | values = rdd.lookup(key). Returns list of values for specific key. Efficient if RDD is partitioned</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>lookup is an action that retrieves values for a specific key</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>How do you handle data skew in Pair RDD operations? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Analyze PRDD-003, PRDD-008, PRDD-013 | Skewed jobs: groupByKey (45s), sortByKey (68s), join (120s). Solutions: salting, repartitioning, broadcast joins</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Data skew causes uneven partition sizes; use salting or adaptive query execution</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is partitionBy? Write code to repartition by key.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>From PRDD-029 | partitioned = rdd.partitionBy(16, hash). Uses hash partitioner to distribute keys</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>partitionBy can improve performance for multiple operations on same keys</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>How do you optimize joins using partitioning? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Compare PRDD-013 (32 partitions) vs PRDD-028 (64 partitions) | Optimized join: 64 partitions reduces time 120s→95s (21% faster). More partitions can reduce skew</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Co-partitioning reduces shuffle in joins</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Aggregating Data with Pair RDDs</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a complete word count example using Pair RDD operations.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Combine operations | lines = sc.textFile('file.txt'); words = lines.flatMap(lambda l: l.split()); word_pairs = words.map(lambda w: (w,1)); counts = word_pairs.reduceByKey(lambda a,b: a+b); counts.saveAsTextFile('output/')</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Word count demonstrates Pair RDD creation and aggregation</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>